--- a/artfynd/A 38158-2025 artfynd.xlsx
+++ b/artfynd/A 38158-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81746625</v>
+        <v>68337154</v>
       </c>
       <c r="B2" t="n">
-        <v>82937</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5589</v>
+        <v>1452</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Timmerskapania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Scapania apiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>Spruce</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lakatjärnbäcken, Jmt</t>
+          <t>Lakatjärnsbäcken drygt 300 m nedströms vägen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557231.7912773519</v>
+        <v>557185</v>
       </c>
       <c r="R2" t="n">
-        <v>6959225.031167146</v>
+        <v>6959302</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-11-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-11-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en stock i bäckkanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,23 +765,120 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Äldre lövrik barrskog intill bäck</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mats Dynesius</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mats Dynesius</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>81746625</v>
+      </c>
+      <c r="B3" t="n">
+        <v>85065</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5589</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rödbrun klubbdyna</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trichoderma nybergianum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lakatjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>557232</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6959225</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre lövrik barrskog intill bäck</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38158-2025 artfynd.xlsx
+++ b/artfynd/A 38158-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68337154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81746625</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>